--- a/GameConfig/Datas/关卡/章节配置表.xlsx
+++ b/GameConfig/Datas/关卡/章节配置表.xlsx
@@ -213,7 +213,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="115">
   <si>
     <t>##var</t>
   </si>
@@ -389,54 +389,6 @@
     <t>Pos</t>
   </si>
   <si>
-    <t>CurrencyType_1</t>
-  </si>
-  <si>
-    <t>BaseNum_1</t>
-  </si>
-  <si>
-    <t>ExtraNum_1</t>
-  </si>
-  <si>
-    <t>CurrencyType_2</t>
-  </si>
-  <si>
-    <t>BaseNum_2</t>
-  </si>
-  <si>
-    <t>ExtraNum_2</t>
-  </si>
-  <si>
-    <t>ItemID_1</t>
-  </si>
-  <si>
-    <t>Num_1</t>
-  </si>
-  <si>
-    <t>ItemID_2</t>
-  </si>
-  <si>
-    <t>Num_2</t>
-  </si>
-  <si>
-    <t>条件章节ID_1</t>
-  </si>
-  <si>
-    <t>条件章节ID_2</t>
-  </si>
-  <si>
-    <t>解锁章节ID_1</t>
-  </si>
-  <si>
-    <t>解锁章节ID_2</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
@@ -470,7 +422,7 @@
     <t>章节图片</t>
   </si>
   <si>
-    <t>章节模型ID</t>
+    <t>章节模型</t>
   </si>
   <si>
     <t>格子图片</t>
@@ -585,6 +537,27 @@
   </si>
   <si>
     <t>刷背包物件的金币基础消耗</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>农场危机</t>
+  </si>
+  <si>
+    <t>shapan_001</t>
+  </si>
+  <si>
+    <t>nongchang</t>
+  </si>
+  <si>
+    <t>main_gezi1</t>
+  </si>
+  <si>
+    <t>怪物如汹涌潮水般汹汹来袭，宁静的农场瞬间陷入危机四伏的境地。小心怪物！</t>
+  </si>
+  <si>
+    <t>无</t>
   </si>
 </sst>
 </file>
@@ -597,7 +570,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -623,6 +596,12 @@
       <b/>
       <sz val="10"/>
       <color theme="0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -768,7 +747,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -795,6 +774,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79955442976165"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -885,12 +882,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -968,7 +959,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -988,6 +979,19 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.349986266670736"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.349986266670736"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.349986266670736"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1107,100 +1111,94 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1209,10 +1207,10 @@
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1221,10 +1219,10 @@
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1233,11 +1231,17 @@
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
@@ -1273,6 +1277,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1599,7 +1618,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BK15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -1609,7 +1628,7 @@
     <col min="9" max="9" width="18.75" style="3" customWidth="1"/>
     <col min="10" max="11" width="18.75" customWidth="1"/>
     <col min="12" max="13" width="18.75" style="4" customWidth="1"/>
-    <col min="14" max="14" width="18.75" style="5" customWidth="1"/>
+    <col min="14" max="14" width="63.625" style="5" customWidth="1"/>
     <col min="15" max="16" width="18.75" style="4" customWidth="1"/>
     <col min="17" max="17" width="21.925" customWidth="1"/>
     <col min="18" max="18" width="15.95" customWidth="1"/>
@@ -1655,7 +1674,7 @@
     <col min="60" max="60" width="27.3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:60">
+    <row r="1" s="1" customFormat="1" spans="1:63">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1815,7 +1834,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:60">
+    <row r="2" s="2" customFormat="1" spans="1:63">
       <c r="A2" s="10" t="s">
         <v>49</v>
       </c>
@@ -1969,9 +1988,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:60">
+    <row r="3" s="2" customFormat="1" spans="1:63">
       <c r="A3" s="10" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -2001,36 +2020,36 @@
       <c r="AA3" s="10"/>
       <c r="AB3" s="10"/>
       <c r="AC3" s="10" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AD3" s="10" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="AE3" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF3" s="10" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="AG3" s="10" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="AH3" s="10" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="AI3" s="10"/>
       <c r="AJ3" s="10"/>
       <c r="AK3" s="10" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="AL3" s="10" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AM3" s="10" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="AN3" s="10" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="AO3" s="10"/>
       <c r="AP3" s="10"/>
@@ -2039,16 +2058,16 @@
       <c r="AS3" s="12"/>
       <c r="AT3" s="10"/>
       <c r="AU3" s="10" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="AV3" s="10" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="AW3" s="10" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AX3" s="10" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="AY3" s="10"/>
       <c r="AZ3" s="10"/>
@@ -2058,16 +2077,16 @@
       <c r="BD3" s="10"/>
       <c r="BE3" s="10"/>
       <c r="BF3" s="10" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="BG3" s="10" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="BH3" s="10"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:60">
+    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:63">
       <c r="A4" s="10" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2129,93 +2148,93 @@
       <c r="BG4" s="6"/>
       <c r="BH4" s="6"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:60">
+    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:63">
       <c r="A5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q5" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="R5" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="S5" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="T5" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="U5" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="V5" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="W5" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="X5" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="Y5" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="Z5" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="AA5" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="AB5" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="AC5" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="T5" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U5" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="V5" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="W5" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="X5" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y5" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z5" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA5" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB5" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC5" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="AD5" s="6"/>
       <c r="AE5" s="6"/>
@@ -2223,127 +2242,240 @@
       <c r="AG5" s="6"/>
       <c r="AH5" s="6"/>
       <c r="AI5" s="6" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="AJ5" s="6" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="AK5" s="6" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="AL5" s="6"/>
       <c r="AM5" s="6"/>
       <c r="AN5" s="6"/>
       <c r="AO5" s="6" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="AP5" s="6" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="AQ5" s="6" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="AR5" s="6" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="AS5" s="13" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="AT5" s="6" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="AU5" s="6" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="AV5" s="6"/>
       <c r="AW5" s="6" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="AX5" s="6"/>
       <c r="AY5" s="6" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="AZ5" s="6" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="BA5" s="6" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="BB5" s="6" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="BC5" s="6" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="BD5" s="6" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="BE5" s="6" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="BF5" s="14" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="BG5" s="6"/>
       <c r="BH5" s="6" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:60">
+    <row r="6" ht="16.5" spans="1:63">
       <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="B6" s="16">
+        <v>10011</v>
+      </c>
+      <c r="C6" s="16">
+        <v>1</v>
+      </c>
+      <c r="D6" s="16">
+        <v>1</v>
+      </c>
+      <c r="E6" s="16">
+        <v>1</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="G6" s="16">
+        <v>10011</v>
+      </c>
       <c r="H6" s="15"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
+      <c r="I6" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>112</v>
+      </c>
       <c r="M6" s="15"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
+      <c r="N6" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="O6" s="16">
+        <v>5</v>
+      </c>
+      <c r="P6" s="16">
+        <v>1</v>
+      </c>
+      <c r="V6" s="16">
+        <v>5</v>
+      </c>
+      <c r="W6" s="16">
+        <v>1</v>
+      </c>
+      <c r="X6" s="16">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="17">
+        <v>4</v>
+      </c>
+      <c r="AD6" s="17">
+        <v>25</v>
+      </c>
+      <c r="AE6" s="17">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="17">
+        <v>2</v>
+      </c>
+      <c r="AG6" s="17">
+        <v>560</v>
+      </c>
+      <c r="AH6" s="17">
+        <v>24</v>
+      </c>
+      <c r="AJ6" s="17">
+        <v>10000</v>
+      </c>
+      <c r="AK6" s="18">
+        <v>99002</v>
+      </c>
+      <c r="AL6" s="17">
+        <v>16</v>
+      </c>
+      <c r="AM6" s="19">
+        <v>5001</v>
+      </c>
+      <c r="AN6" s="17">
+        <v>5</v>
+      </c>
+      <c r="AO6" s="19">
+        <v>100114</v>
+      </c>
+      <c r="AP6" s="17">
+        <v>5</v>
+      </c>
+      <c r="AQ6" s="19">
+        <v>100115</v>
+      </c>
+      <c r="AS6" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="AU6" s="20">
+        <v>10012</v>
+      </c>
+      <c r="AZ6" s="17">
+        <v>1</v>
+      </c>
+      <c r="BA6" s="17">
+        <v>1</v>
+      </c>
+      <c r="BB6" s="17">
+        <v>1</v>
+      </c>
+      <c r="BC6" s="17">
+        <v>1</v>
+      </c>
+      <c r="BD6" s="17">
+        <v>1</v>
+      </c>
+      <c r="BE6" s="17">
+        <v>1</v>
+      </c>
+      <c r="BF6" s="17">
+        <v>3</v>
+      </c>
+      <c r="BG6" s="17">
+        <v>-3.5</v>
+      </c>
+      <c r="BH6" s="17">
+        <v>15</v>
+      </c>
+      <c r="BI6" s="17"/>
+      <c r="BJ6" s="17"/>
+      <c r="BK6" s="17"/>
     </row>
-    <row r="7" spans="1:60">
+    <row r="7" spans="1:63">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
-      <c r="I7" s="17"/>
+      <c r="I7" s="22"/>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
-      <c r="N7" s="17"/>
+      <c r="N7" s="22"/>
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:60">
+    <row r="8" spans="1:63">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
-      <c r="I8" s="17"/>
+      <c r="I8" s="22"/>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
-      <c r="N8" s="17"/>
+      <c r="N8" s="22"/>
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
     </row>
-    <row r="9" spans="1:60">
+    <row r="9" spans="1:63">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -2352,16 +2484,16 @@
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
-      <c r="I9" s="17"/>
+      <c r="I9" s="22"/>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
-      <c r="N9" s="17"/>
+      <c r="N9" s="22"/>
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:60">
+    <row r="10" spans="1:63">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -2370,34 +2502,34 @@
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
-      <c r="I10" s="17"/>
+      <c r="I10" s="22"/>
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
-      <c r="N10" s="17"/>
+      <c r="N10" s="22"/>
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
     </row>
-    <row r="11" spans="1:60">
+    <row r="11" spans="1:63">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
-      <c r="I11" s="17"/>
+      <c r="I11" s="22"/>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
-      <c r="N11" s="17"/>
+      <c r="N11" s="22"/>
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
     </row>
-    <row r="12" spans="1:60">
+    <row r="12" spans="1:63">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -2406,66 +2538,66 @@
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
-      <c r="I12" s="17"/>
+      <c r="I12" s="22"/>
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
-      <c r="N12" s="17"/>
+      <c r="N12" s="22"/>
       <c r="O12" s="15"/>
       <c r="P12" s="15"/>
     </row>
-    <row r="13" spans="1:60">
+    <row r="13" spans="1:63">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
-      <c r="I13" s="17"/>
+      <c r="I13" s="22"/>
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
-      <c r="N13" s="17"/>
+      <c r="N13" s="22"/>
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
     </row>
-    <row r="14" spans="1:60">
+    <row r="14" spans="1:63">
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
-      <c r="I14" s="17"/>
+      <c r="I14" s="22"/>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
-      <c r="N14" s="17"/>
+      <c r="N14" s="22"/>
       <c r="O14" s="15"/>
       <c r="P14" s="15"/>
     </row>
-    <row r="15" spans="1:60">
+    <row r="15" spans="1:63">
       <c r="A15" s="15"/>
       <c r="B15" s="15"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
-      <c r="I15" s="17"/>
+      <c r="I15" s="22"/>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
-      <c r="N15" s="17"/>
+      <c r="N15" s="22"/>
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
     </row>

--- a/GameConfig/Datas/关卡/章节配置表.xlsx
+++ b/GameConfig/Datas/关卡/章节配置表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\关卡\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA109996-6899-4D4A-BD96-C7F65F6E1AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Jun</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -47,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -72,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -94,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0">
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -117,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0">
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -139,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -162,7 +168,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0">
+    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -185,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="0">
+    <comment ref="AJ1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -563,14 +569,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -606,136 +606,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -746,8 +616,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -768,198 +651,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79955442976165"/>
+        <fgColor theme="9" tint="0.79952391125217448"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799340800195319"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -984,267 +699,31 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1252,27 +731,27 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="22" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="22" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="23" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="23" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1299,62 +778,32 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="3">
+    <cellStyle name="差" xfId="2" builtinId="27"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1612,69 +1061,69 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BK15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
-    <col min="2" max="2" width="17.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
     <col min="3" max="5" width="22.5" customWidth="1"/>
     <col min="6" max="8" width="18.75" customWidth="1"/>
     <col min="9" max="9" width="18.75" style="3" customWidth="1"/>
     <col min="10" max="11" width="18.75" customWidth="1"/>
     <col min="12" max="13" width="18.75" style="4" customWidth="1"/>
-    <col min="14" max="14" width="63.625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="63.58203125" style="5" customWidth="1"/>
     <col min="15" max="16" width="18.75" style="4" customWidth="1"/>
-    <col min="17" max="17" width="21.925" customWidth="1"/>
-    <col min="18" max="18" width="15.95" customWidth="1"/>
-    <col min="19" max="19" width="17.975" customWidth="1"/>
+    <col min="17" max="17" width="21.9140625" customWidth="1"/>
+    <col min="18" max="18" width="15.9140625" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="20" customWidth="1"/>
-    <col min="21" max="21" width="20.7583333333333" customWidth="1"/>
-    <col min="22" max="22" width="15.1916666666667" customWidth="1"/>
+    <col min="21" max="21" width="20.75" customWidth="1"/>
+    <col min="22" max="22" width="15.1640625" customWidth="1"/>
     <col min="23" max="23" width="26.25" customWidth="1"/>
-    <col min="24" max="24" width="17.4" customWidth="1"/>
-    <col min="25" max="25" width="14.125" customWidth="1"/>
-    <col min="26" max="26" width="17.6916666666667" customWidth="1"/>
-    <col min="27" max="27" width="19.9916666666667" customWidth="1"/>
-    <col min="28" max="28" width="25.475" customWidth="1"/>
-    <col min="29" max="29" width="22.5833333333333" customWidth="1"/>
-    <col min="30" max="30" width="14.6166666666667" customWidth="1"/>
-    <col min="31" max="31" width="12.0083333333333" customWidth="1"/>
-    <col min="32" max="32" width="15.1833333333333" customWidth="1"/>
-    <col min="33" max="33" width="12.3" customWidth="1"/>
-    <col min="34" max="34" width="13.8416666666667" customWidth="1"/>
-    <col min="35" max="35" width="13.55" customWidth="1"/>
-    <col min="36" max="36" width="17.4" customWidth="1"/>
-    <col min="37" max="37" width="24.3166666666667" customWidth="1"/>
-    <col min="39" max="39" width="13.2666666666667" customWidth="1"/>
-    <col min="40" max="40" width="12.7833333333333" customWidth="1"/>
-    <col min="41" max="41" width="12.6916666666667" customWidth="1"/>
-    <col min="42" max="42" width="19.6083333333333" customWidth="1"/>
-    <col min="43" max="43" width="12.4916666666667" customWidth="1"/>
-    <col min="44" max="44" width="24.125" customWidth="1"/>
-    <col min="45" max="45" width="15.375" style="3" customWidth="1"/>
-    <col min="46" max="46" width="14.9" customWidth="1"/>
-    <col min="47" max="47" width="19.7083333333333" customWidth="1"/>
-    <col min="48" max="49" width="26.0583333333333" customWidth="1"/>
-    <col min="50" max="50" width="18.9416666666667" customWidth="1"/>
+    <col min="24" max="24" width="17.4140625" customWidth="1"/>
+    <col min="25" max="25" width="14.08203125" customWidth="1"/>
+    <col min="26" max="26" width="17.6640625" customWidth="1"/>
+    <col min="27" max="27" width="20" customWidth="1"/>
+    <col min="28" max="28" width="25.5" customWidth="1"/>
+    <col min="29" max="29" width="22.58203125" customWidth="1"/>
+    <col min="30" max="30" width="14.58203125" customWidth="1"/>
+    <col min="31" max="31" width="12" customWidth="1"/>
+    <col min="32" max="32" width="15.1640625" customWidth="1"/>
+    <col min="33" max="33" width="12.33203125" customWidth="1"/>
+    <col min="34" max="34" width="13.83203125" customWidth="1"/>
+    <col min="35" max="35" width="13.58203125" customWidth="1"/>
+    <col min="36" max="36" width="17.4140625" customWidth="1"/>
+    <col min="37" max="37" width="24.33203125" customWidth="1"/>
+    <col min="39" max="39" width="13.25" customWidth="1"/>
+    <col min="40" max="40" width="12.75" customWidth="1"/>
+    <col min="41" max="41" width="12.6640625" customWidth="1"/>
+    <col min="42" max="42" width="19.58203125" customWidth="1"/>
+    <col min="43" max="43" width="12.5" customWidth="1"/>
+    <col min="44" max="44" width="24.08203125" customWidth="1"/>
+    <col min="45" max="45" width="15.33203125" style="3" customWidth="1"/>
+    <col min="46" max="46" width="14.9140625" customWidth="1"/>
+    <col min="47" max="47" width="19.6640625" customWidth="1"/>
+    <col min="48" max="49" width="26.08203125" customWidth="1"/>
+    <col min="50" max="50" width="18.9140625" customWidth="1"/>
     <col min="51" max="51" width="17.5" customWidth="1"/>
-    <col min="52" max="52" width="13.3583333333333" customWidth="1"/>
-    <col min="53" max="53" width="21.5333333333333" customWidth="1"/>
-    <col min="54" max="54" width="20.8583333333333" customWidth="1"/>
-    <col min="55" max="55" width="19.3166666666667" customWidth="1"/>
-    <col min="56" max="56" width="28.075" customWidth="1"/>
-    <col min="57" max="57" width="19.9" customWidth="1"/>
-    <col min="58" max="58" width="15.6666666666667" customWidth="1"/>
-    <col min="59" max="59" width="17.1083333333333" customWidth="1"/>
-    <col min="60" max="60" width="27.3" customWidth="1"/>
+    <col min="52" max="52" width="13.33203125" customWidth="1"/>
+    <col min="53" max="53" width="21.5" customWidth="1"/>
+    <col min="54" max="54" width="20.83203125" customWidth="1"/>
+    <col min="55" max="55" width="19.33203125" customWidth="1"/>
+    <col min="56" max="56" width="28.08203125" customWidth="1"/>
+    <col min="57" max="57" width="19.9140625" customWidth="1"/>
+    <col min="58" max="58" width="15.6640625" customWidth="1"/>
+    <col min="59" max="59" width="17.08203125" customWidth="1"/>
+    <col min="60" max="60" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:63">
+    <row r="1" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1759,26 +1208,26 @@
       <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="6"/>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="6"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="23"/>
+      <c r="AH1" s="23"/>
       <c r="AI1" s="6" t="s">
         <v>29</v>
       </c>
       <c r="AJ1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AK1" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="AL1" s="6"/>
-      <c r="AM1" s="6"/>
-      <c r="AN1" s="6"/>
+      <c r="AL1" s="23"/>
+      <c r="AM1" s="23"/>
+      <c r="AN1" s="23"/>
       <c r="AO1" s="6" t="s">
         <v>32</v>
       </c>
@@ -1797,14 +1246,14 @@
       <c r="AT1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AU1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="AV1" s="6"/>
-      <c r="AW1" s="6" t="s">
+      <c r="AV1" s="23"/>
+      <c r="AW1" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="6"/>
+      <c r="AX1" s="23"/>
       <c r="AY1" s="6" t="s">
         <v>40</v>
       </c>
@@ -1826,15 +1275,15 @@
       <c r="BE1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BF1" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="BG1" s="6"/>
+      <c r="BG1" s="23"/>
       <c r="BH1" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:63">
+    <row r="2" spans="1:63" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>49</v>
       </c>
@@ -1915,26 +1364,26 @@
       <c r="AB2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AC2" s="10" t="s">
+      <c r="AC2" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AD2" s="10"/>
-      <c r="AE2" s="10"/>
-      <c r="AF2" s="10"/>
-      <c r="AG2" s="10"/>
-      <c r="AH2" s="10"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
+      <c r="AH2" s="24"/>
       <c r="AI2" s="10" t="s">
         <v>50</v>
       </c>
       <c r="AJ2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AK2" s="10" t="s">
+      <c r="AK2" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="AL2" s="10"/>
-      <c r="AM2" s="10"/>
-      <c r="AN2" s="10"/>
+      <c r="AL2" s="24"/>
+      <c r="AM2" s="24"/>
+      <c r="AN2" s="24"/>
       <c r="AO2" s="10" t="s">
         <v>50</v>
       </c>
@@ -1951,14 +1400,14 @@
       <c r="AT2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="AU2" s="10" t="s">
+      <c r="AU2" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="AV2" s="10"/>
-      <c r="AW2" s="10" t="s">
+      <c r="AV2" s="24"/>
+      <c r="AW2" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="AX2" s="10"/>
+      <c r="AX2" s="24"/>
       <c r="AY2" s="10" t="s">
         <v>50</v>
       </c>
@@ -1980,15 +1429,15 @@
       <c r="BE2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="BF2" s="10" t="s">
+      <c r="BF2" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="BG2" s="10"/>
+      <c r="BG2" s="24"/>
       <c r="BH2" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:63">
+    <row r="3" spans="1:63" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>49</v>
       </c>
@@ -2084,7 +1533,7 @@
       </c>
       <c r="BH3" s="10"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:63">
+    <row r="4" spans="1:63" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>58</v>
       </c>
@@ -2148,7 +1597,7 @@
       <c r="BG4" s="6"/>
       <c r="BH4" s="6"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:63">
+    <row r="5" spans="1:63" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>59</v>
       </c>
@@ -2233,26 +1682,26 @@
       <c r="AB5" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="AC5" s="6" t="s">
+      <c r="AC5" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
-      <c r="AG5" s="6"/>
-      <c r="AH5" s="6"/>
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="23"/>
+      <c r="AF5" s="23"/>
+      <c r="AG5" s="23"/>
+      <c r="AH5" s="23"/>
       <c r="AI5" s="6" t="s">
         <v>88</v>
       </c>
       <c r="AJ5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AK5" s="6" t="s">
+      <c r="AK5" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="AL5" s="6"/>
-      <c r="AM5" s="6"/>
-      <c r="AN5" s="6"/>
+      <c r="AL5" s="23"/>
+      <c r="AM5" s="23"/>
+      <c r="AN5" s="23"/>
       <c r="AO5" s="6" t="s">
         <v>91</v>
       </c>
@@ -2271,14 +1720,14 @@
       <c r="AT5" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="AU5" s="6" t="s">
+      <c r="AU5" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="AV5" s="6"/>
-      <c r="AW5" s="6" t="s">
+      <c r="AV5" s="23"/>
+      <c r="AW5" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="AX5" s="6"/>
+      <c r="AX5" s="23"/>
       <c r="AY5" s="6" t="s">
         <v>99</v>
       </c>
@@ -2300,15 +1749,15 @@
       <c r="BE5" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="BF5" s="14" t="s">
+      <c r="BF5" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="BG5" s="6"/>
+      <c r="BG5" s="23"/>
       <c r="BH5" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:63">
+    <row r="6" spans="1:63" ht="15" x14ac:dyDescent="0.4">
       <c r="A6" s="15"/>
       <c r="B6" s="16">
         <v>10011</v>
@@ -2359,6 +1808,12 @@
       </c>
       <c r="X6" s="16">
         <v>1</v>
+      </c>
+      <c r="AA6" s="26">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="26">
+        <v>2</v>
       </c>
       <c r="AC6" s="17">
         <v>4</v>
@@ -2439,7 +1894,7 @@
       <c r="BJ6" s="17"/>
       <c r="BK6" s="17"/>
     </row>
-    <row r="7" spans="1:63">
+    <row r="7" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="21"/>
@@ -2457,7 +1912,7 @@
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:63">
+    <row r="8" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="21"/>
@@ -2475,7 +1930,7 @@
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
     </row>
-    <row r="9" spans="1:63">
+    <row r="9" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -2493,7 +1948,7 @@
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:63">
+    <row r="10" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -2511,7 +1966,7 @@
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
     </row>
-    <row r="11" spans="1:63">
+    <row r="11" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="21"/>
@@ -2529,7 +1984,7 @@
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
     </row>
-    <row r="12" spans="1:63">
+    <row r="12" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -2547,7 +2002,7 @@
       <c r="O12" s="15"/>
       <c r="P12" s="15"/>
     </row>
-    <row r="13" spans="1:63">
+    <row r="13" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="21"/>
@@ -2565,7 +2020,7 @@
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
     </row>
-    <row r="14" spans="1:63">
+    <row r="14" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
       <c r="C14" s="21"/>
@@ -2583,7 +2038,7 @@
       <c r="O14" s="15"/>
       <c r="P14" s="15"/>
     </row>
-    <row r="15" spans="1:63">
+    <row r="15" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A15" s="15"/>
       <c r="B15" s="15"/>
       <c r="C15" s="21"/>
@@ -2603,25 +2058,25 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="AC5:AH5"/>
+    <mergeCell ref="AK5:AN5"/>
+    <mergeCell ref="AU5:AV5"/>
+    <mergeCell ref="AW5:AX5"/>
+    <mergeCell ref="BF5:BG5"/>
+    <mergeCell ref="AC2:AH2"/>
+    <mergeCell ref="AK2:AN2"/>
+    <mergeCell ref="AU2:AV2"/>
+    <mergeCell ref="AW2:AX2"/>
+    <mergeCell ref="BF2:BG2"/>
     <mergeCell ref="AC1:AH1"/>
     <mergeCell ref="AK1:AN1"/>
     <mergeCell ref="AU1:AV1"/>
     <mergeCell ref="AW1:AX1"/>
     <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="AC2:AH2"/>
-    <mergeCell ref="AK2:AN2"/>
-    <mergeCell ref="AU2:AV2"/>
-    <mergeCell ref="AW2:AX2"/>
-    <mergeCell ref="BF2:BG2"/>
-    <mergeCell ref="AC5:AH5"/>
-    <mergeCell ref="AK5:AN5"/>
-    <mergeCell ref="AU5:AV5"/>
-    <mergeCell ref="AW5:AX5"/>
-    <mergeCell ref="BF5:BG5"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/GameConfig/Datas/关卡/章节配置表.xlsx
+++ b/GameConfig/Datas/关卡/章节配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\GitHub_Project\DGame_Fantasy\GameConfig\Datas\关卡\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA109996-6899-4D4A-BD96-C7F65F6E1AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8F4E27-5FE2-4E70-A1C8-496965B24FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,6 +44,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">ps:
@@ -60,6 +61,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>ps:</t>
@@ -68,6 +70,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -85,6 +88,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>ps:</t>
@@ -93,6 +97,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -107,6 +112,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>ps:</t>
@@ -115,6 +121,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -130,6 +137,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">ps:
@@ -139,6 +147,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>累计失败达X次后，下一次开始衰减</t>
@@ -152,6 +161,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>ps:</t>
@@ -160,6 +170,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -175,6 +186,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>ps:</t>
@@ -183,6 +195,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -198,6 +211,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>ps:</t>
@@ -206,6 +220,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -548,22 +563,25 @@
     <t>1</t>
   </si>
   <si>
+    <t>shapan_001</t>
+  </si>
+  <si>
+    <t>nongchang</t>
+  </si>
+  <si>
+    <t>main_gezi1</t>
+  </si>
+  <si>
     <t>农场危机</t>
-  </si>
-  <si>
-    <t>shapan_001</t>
-  </si>
-  <si>
-    <t>nongchang</t>
-  </si>
-  <si>
-    <t>main_gezi1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>怪物如汹涌潮水般汹汹来袭，宁静的农场瞬间陷入危机四伏的境地。小心怪物！</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>无</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -582,6 +600,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -589,6 +608,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -597,28 +617,33 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -778,17 +803,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1208,26 +1233,26 @@
       <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="23" t="s">
+      <c r="AC1" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="23"/>
-      <c r="AE1" s="23"/>
-      <c r="AF1" s="23"/>
-      <c r="AG1" s="23"/>
-      <c r="AH1" s="23"/>
+      <c r="AD1" s="24"/>
+      <c r="AE1" s="24"/>
+      <c r="AF1" s="24"/>
+      <c r="AG1" s="24"/>
+      <c r="AH1" s="24"/>
       <c r="AI1" s="6" t="s">
         <v>29</v>
       </c>
       <c r="AJ1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AK1" s="23" t="s">
+      <c r="AK1" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="AL1" s="23"/>
-      <c r="AM1" s="23"/>
-      <c r="AN1" s="23"/>
+      <c r="AL1" s="24"/>
+      <c r="AM1" s="24"/>
+      <c r="AN1" s="24"/>
       <c r="AO1" s="6" t="s">
         <v>32</v>
       </c>
@@ -1246,14 +1271,14 @@
       <c r="AT1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AU1" s="23" t="s">
+      <c r="AU1" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="AV1" s="23"/>
-      <c r="AW1" s="23" t="s">
+      <c r="AV1" s="24"/>
+      <c r="AW1" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="23"/>
+      <c r="AX1" s="24"/>
       <c r="AY1" s="6" t="s">
         <v>40</v>
       </c>
@@ -1275,10 +1300,10 @@
       <c r="BE1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="BF1" s="23" t="s">
+      <c r="BF1" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BG1" s="23"/>
+      <c r="BG1" s="24"/>
       <c r="BH1" s="6" t="s">
         <v>48</v>
       </c>
@@ -1364,26 +1389,26 @@
       <c r="AB2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AC2" s="24" t="s">
+      <c r="AC2" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="26"/>
+      <c r="AG2" s="26"/>
+      <c r="AH2" s="26"/>
       <c r="AI2" s="10" t="s">
         <v>50</v>
       </c>
       <c r="AJ2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AK2" s="24" t="s">
+      <c r="AK2" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="24"/>
-      <c r="AN2" s="24"/>
+      <c r="AL2" s="26"/>
+      <c r="AM2" s="26"/>
+      <c r="AN2" s="26"/>
       <c r="AO2" s="10" t="s">
         <v>50</v>
       </c>
@@ -1400,14 +1425,14 @@
       <c r="AT2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="AU2" s="24" t="s">
+      <c r="AU2" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="AV2" s="24"/>
-      <c r="AW2" s="24" t="s">
+      <c r="AV2" s="26"/>
+      <c r="AW2" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="AX2" s="24"/>
+      <c r="AX2" s="26"/>
       <c r="AY2" s="10" t="s">
         <v>50</v>
       </c>
@@ -1429,10 +1454,10 @@
       <c r="BE2" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="BF2" s="24" t="s">
+      <c r="BF2" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="BG2" s="24"/>
+      <c r="BG2" s="26"/>
       <c r="BH2" s="10" t="s">
         <v>50</v>
       </c>
@@ -1682,26 +1707,26 @@
       <c r="AB5" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="AC5" s="23" t="s">
+      <c r="AC5" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="AD5" s="23"/>
-      <c r="AE5" s="23"/>
-      <c r="AF5" s="23"/>
-      <c r="AG5" s="23"/>
-      <c r="AH5" s="23"/>
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="24"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="24"/>
       <c r="AI5" s="6" t="s">
         <v>88</v>
       </c>
       <c r="AJ5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AK5" s="23" t="s">
+      <c r="AK5" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="AL5" s="23"/>
-      <c r="AM5" s="23"/>
-      <c r="AN5" s="23"/>
+      <c r="AL5" s="24"/>
+      <c r="AM5" s="24"/>
+      <c r="AN5" s="24"/>
       <c r="AO5" s="6" t="s">
         <v>91</v>
       </c>
@@ -1720,14 +1745,14 @@
       <c r="AT5" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="AU5" s="23" t="s">
+      <c r="AU5" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="AV5" s="23"/>
-      <c r="AW5" s="23" t="s">
+      <c r="AV5" s="24"/>
+      <c r="AW5" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="AX5" s="23"/>
+      <c r="AX5" s="24"/>
       <c r="AY5" s="6" t="s">
         <v>99</v>
       </c>
@@ -1752,7 +1777,7 @@
       <c r="BF5" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="BG5" s="23"/>
+      <c r="BG5" s="24"/>
       <c r="BH5" s="6" t="s">
         <v>107</v>
       </c>
@@ -1777,20 +1802,24 @@
       <c r="G6" s="16">
         <v>10011</v>
       </c>
-      <c r="H6" s="15"/>
+      <c r="H6" s="15">
+        <v>10200001</v>
+      </c>
       <c r="I6" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="J6" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="K6" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="L6" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="L6" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="M6" s="15"/>
+      <c r="M6" s="15">
+        <v>10200002</v>
+      </c>
       <c r="N6" s="16" t="s">
         <v>113</v>
       </c>
@@ -1809,10 +1838,10 @@
       <c r="X6" s="16">
         <v>1</v>
       </c>
-      <c r="AA6" s="26">
+      <c r="AA6" s="23">
         <v>1</v>
       </c>
-      <c r="AB6" s="26">
+      <c r="AB6" s="23">
         <v>2</v>
       </c>
       <c r="AC6" s="17">
@@ -1856,6 +1885,9 @@
       </c>
       <c r="AQ6" s="19">
         <v>100115</v>
+      </c>
+      <c r="AR6" s="17">
+        <v>11000003</v>
       </c>
       <c r="AS6" s="17" t="s">
         <v>114</v>
@@ -2058,21 +2090,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="AK1:AN1"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AW1:AX1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="AC2:AH2"/>
+    <mergeCell ref="AK2:AN2"/>
+    <mergeCell ref="AU2:AV2"/>
+    <mergeCell ref="AW2:AX2"/>
+    <mergeCell ref="BF2:BG2"/>
     <mergeCell ref="AC5:AH5"/>
     <mergeCell ref="AK5:AN5"/>
     <mergeCell ref="AU5:AV5"/>
     <mergeCell ref="AW5:AX5"/>
     <mergeCell ref="BF5:BG5"/>
-    <mergeCell ref="AC2:AH2"/>
-    <mergeCell ref="AK2:AN2"/>
-    <mergeCell ref="AU2:AV2"/>
-    <mergeCell ref="AW2:AX2"/>
-    <mergeCell ref="BF2:BG2"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="AK1:AN1"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AW1:AX1"/>
-    <mergeCell ref="BF1:BG1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
